--- a/Result/profitability/3229.xlsx
+++ b/Result/profitability/3229.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.09</v>
       </c>
       <c r="M2" t="n">
-        <v>0.006250000000000002</v>
+        <v>0.12125</v>
       </c>
       <c r="N2" t="n">
-        <v>7.76625</v>
+        <v>9.21875</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.28</v>
       </c>
       <c r="M3" t="n">
-        <v>0.065</v>
+        <v>0.1525</v>
       </c>
       <c r="N3" t="n">
-        <v>9.404999999999999</v>
+        <v>10.545</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.17875</v>
+        <v>0.26125</v>
       </c>
       <c r="N4" t="n">
-        <v>11.06875</v>
+        <v>12.0225</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,16 +1018,16 @@
         <v>-0.11</v>
       </c>
       <c r="M5" t="n">
-        <v>0.15625</v>
+        <v>0.31625</v>
       </c>
       <c r="N5" t="n">
-        <v>11.58</v>
+        <v>12.92625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>0.24</v>
+        <v>0.3412499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>13.055</v>
+        <v>14.5725</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.12</v>
       </c>
       <c r="M7" t="n">
-        <v>0.235</v>
+        <v>0.31</v>
       </c>
       <c r="N7" t="n">
-        <v>14.23875</v>
+        <v>14.8075</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.22</v>
       </c>
       <c r="M8" t="n">
-        <v>0.24625</v>
+        <v>0.26875</v>
       </c>
       <c r="N8" t="n">
-        <v>15.34375</v>
+        <v>15.8525</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -2026,7 +2026,7 @@
         <v>-0.14</v>
       </c>
       <c r="M13" t="n">
-        <v>0.09875</v>
+        <v>0.09874999999999998</v>
       </c>
       <c r="N13" t="n">
         <v>14.57125</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3229</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>413</v>
+      </c>
+      <c r="D75" t="n">
+        <v>351</v>
+      </c>
+      <c r="E75" t="n">
+        <v>62</v>
+      </c>
+      <c r="F75" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="G75" t="n">
+        <v>45</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.01%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>46</v>
+      </c>
+      <c r="K75" t="n">
+        <v>47</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.08624999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>7.5425</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1799999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3272727272727272</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.069999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3713503649635035</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.327272727272727</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>2.528169014084507</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
